--- a/DPO/Template_DPO.xlsx
+++ b/DPO/Template_DPO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UTC2\DoAnTotNghiep\DPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898C3FB2-E49A-4F28-A29C-9AA07C6E640A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E185099-3D58-41EF-8007-BF559B46D1AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{F1034444-0232-486D-96CF-65F521278E31}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1034444-0232-486D-96CF-65F521278E31}"/>
   </bookViews>
   <sheets>
     <sheet name="DPO Template" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="39">
   <si>
     <t>(*)</t>
   </si>
@@ -51,51 +51,6 @@
   </si>
   <si>
     <t>Mandatory if "SP code" is blank</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">DISTRIBUTOR PURCHASE ORDER (DPO)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="15"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>ĐƠN ĐẶT HÀNG</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>DPO No. *</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Số DPO</t>
-    </r>
   </si>
   <si>
     <r>
@@ -328,35 +283,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>DPO remarks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ghi chú</t>
-    </r>
-  </si>
-  <si>
     <t>Customer type
 (**)</t>
   </si>
@@ -405,13 +331,31 @@
     <t>CR-Y120</t>
   </si>
   <si>
-    <t>xxxxxxx1</t>
-  </si>
-  <si>
     <t>Test Material code1</t>
   </si>
   <si>
     <t>CÔNG TY 3 test</t>
+  </si>
+  <si>
+    <t>PP.FA_26.06_005</t>
+  </si>
+  <si>
+    <t>DPO remarks</t>
+  </si>
+  <si>
+    <t>DPO No. *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISTRIBUTOR PURCHASE ORDER </t>
+  </si>
+  <si>
+    <t>xxxxxxx2</t>
+  </si>
+  <si>
+    <t>FAKE-SC-E1-01</t>
+  </si>
+  <si>
+    <t>SC-E1-4-0.4K</t>
   </si>
 </sst>
 </file>
@@ -441,7 +385,7 @@
     <numFmt numFmtId="178" formatCode="_ &quot;kr&quot;\ * #,##0_ ;_ &quot;kr&quot;\ * \-#,##0_ ;_ &quot;kr&quot;\ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;kr&quot;\ * #,##0.00_ ;_ &quot;kr&quot;\ * \-#,##0.00_ ;_ &quot;kr&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="98">
+  <fonts count="96">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -901,25 +845,7 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="15"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1066,6 +992,13 @@
     <font>
       <sz val="8"/>
       <color rgb="FF495057"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFF9F38"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1811,30 +1744,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="38" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="38" fontId="77" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="81" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="78" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="72" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1844,7 +1777,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="175" fontId="65" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1871,7 +1804,7 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="10" fontId="25" fillId="43" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
@@ -1889,34 +1822,34 @@
     <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
@@ -1925,7 +1858,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -1935,71 +1868,71 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
@@ -2015,19 +1948,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="77" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="77" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="77" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="28" fillId="0" borderId="0">
@@ -2088,8 +2021,8 @@
     <xf numFmtId="0" fontId="49" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="80" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="77" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -2119,10 +2052,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="40" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="85" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="82" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="79" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="76" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2131,7 +2064,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="41" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="41" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0">
@@ -2141,19 +2074,19 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -2200,112 +2133,115 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="46" borderId="21" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="47" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="46" borderId="21" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="47" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="47" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="47" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="9" xfId="267" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="9" xfId="267" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="91" fillId="0" borderId="0" xfId="57" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="88" fillId="0" borderId="0" xfId="57" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="267" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="267" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="267" applyFont="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="267" applyFont="1"/>
+    <xf numFmtId="0" fontId="86" fillId="48" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="48" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="89" fillId="48" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="48" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="48" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="89" fillId="48" borderId="9" xfId="57" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="37" fontId="89" fillId="48" borderId="9" xfId="267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="48" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="9" xfId="267" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="86" fillId="48" borderId="9" xfId="57" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="86" fillId="48" borderId="9" xfId="267" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="48" borderId="9" xfId="267" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="9" xfId="267" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="37" fontId="90" fillId="0" borderId="9" xfId="267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="37" fontId="87" fillId="0" borderId="9" xfId="267" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="46" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="46" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="46" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="46" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="46" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="46" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="46" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="86" fillId="46" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="3" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7767,15 +7703,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="40.950000000000003" customHeight="1">
-      <c r="C1" s="27" t="s">
-        <v>6</v>
+      <c r="C1" s="28" t="s">
+        <v>35</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
       <c r="P1" s="3" t="s">
         <v>3</v>
       </c>
@@ -7785,23 +7721,23 @@
       <c r="P2" s="5"/>
       <c r="Q2" s="6"/>
       <c r="U2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="30.6" customHeight="1">
-      <c r="A3" s="28" t="s">
-        <v>7</v>
+      <c r="A3" s="29" t="s">
+        <v>34</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="32" t="s">
-        <v>33</v>
+      <c r="B3" s="30"/>
+      <c r="C3" s="33" t="s">
+        <v>36</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="34"/>
       <c r="P3" s="5" t="s">
         <v>0</v>
       </c>
@@ -7809,21 +7745,21 @@
         <v>1</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" thickBot="1">
-      <c r="A4" s="30" t="s">
-        <v>21</v>
+      <c r="A4" s="31" t="s">
+        <v>33</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="35"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="36"/>
       <c r="P4" s="5" t="s">
         <v>4</v>
       </c>
@@ -7831,7 +7767,7 @@
         <v>5</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="16.2" thickBot="1">
@@ -7849,68 +7785,68 @@
         <v>2</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="34.950000000000003" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
       <c r="U6" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="46.8">
       <c r="A7" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="F7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="I7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="J7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="K7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="M7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>19</v>
-      </c>
       <c r="U7" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -7918,10 +7854,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="18"/>
@@ -7930,25 +7866,25 @@
         <v>10</v>
       </c>
       <c r="H8" s="20">
-        <v>450000</v>
+        <v>480000</v>
       </c>
       <c r="I8" s="21">
         <f>IF(G8*H8=0,"",G8*H8)</f>
-        <v>4500000</v>
+        <v>4800000</v>
       </c>
       <c r="J8" s="18"/>
-      <c r="K8" s="36" t="s">
-        <v>35</v>
+      <c r="K8" s="24" t="s">
+        <v>31</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="24">
         <v>2300852009</v>
       </c>
       <c r="M8" s="22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N8" s="22"/>
       <c r="U8" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -7956,53 +7892,73 @@
         <v>2</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
+      <c r="F9" s="19" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" s="17">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H9" s="20">
-        <v>1036000</v>
+        <v>1000000</v>
       </c>
       <c r="I9" s="21">
         <f t="shared" ref="I9:I17" si="0">IF(G9*H9=0,"",G9*H9)</f>
-        <v>15540000</v>
+        <v>9000000</v>
       </c>
       <c r="J9" s="18"/>
-      <c r="K9" s="36" t="s">
-        <v>35</v>
+      <c r="K9" s="24" t="s">
+        <v>31</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="24">
         <v>2300852009</v>
       </c>
       <c r="M9" s="22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N9" s="22"/>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
+      <c r="A10" s="17">
+        <v>3</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="21" t="str">
+      <c r="F10" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="17">
+        <v>15</v>
+      </c>
+      <c r="H10" s="37">
+        <v>8000000</v>
+      </c>
+      <c r="I10" s="21">
         <f t="shared" si="0"/>
-        <v/>
+        <v>120000000</v>
       </c>
       <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
+      <c r="K10" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10" s="24">
+        <v>2300852009</v>
+      </c>
+      <c r="M10" s="22" t="s">
+        <v>25</v>
+      </c>
       <c r="N10" s="22"/>
     </row>
     <row r="11" spans="1:21">
@@ -8139,23 +8095,23 @@
       <c r="N17" s="22"/>
     </row>
     <row r="18" spans="1:14" ht="41.55" customHeight="1">
-      <c r="A18" s="24" t="s">
-        <v>20</v>
+      <c r="A18" s="25" t="s">
+        <v>18</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
       <c r="G18" s="13">
         <f>SUM(G8:G17)</f>
-        <v>25</v>
+        <v>34</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="26">
         <f>SUM(I8:I17)</f>
-        <v>20040000</v>
+        <v>133800000</v>
       </c>
-      <c r="I18" s="25"/>
+      <c r="I18" s="26"/>
       <c r="J18" s="14"/>
       <c r="K18" s="15"/>
       <c r="L18" s="16"/>
@@ -8173,7 +8129,7 @@
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="C4:I4"/>
   </mergeCells>
-  <phoneticPr fontId="96" type="noConversion"/>
+  <phoneticPr fontId="93" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M8:M65544" xr:uid="{44E3A4C7-08A3-4678-A05D-ECE29E0F8BE1}">
       <formula1>$U$2:$U$8</formula1>
